--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/DISTRICT_OF_COLUMBIA_2019.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/DISTRICT_OF_COLUMBIA_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D156"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -384,7 +384,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>San José de Gracia</t>
+          <t>San José De Gracia</t>
         </is>
       </c>
       <c r="C2">
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Bella Vista</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>San Lucas</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -605,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Total</t>
@@ -667,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -682,7 +757,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -698,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -711,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -724,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -737,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -750,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -763,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -776,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -789,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -802,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -815,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Total</t>
@@ -846,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -861,12 +991,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Almoloya de Juárez</t>
+          <t>Almoloya De Juárez</t>
         </is>
       </c>
       <c r="C36">
@@ -877,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Chalco</t>
@@ -890,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -903,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -916,9 +1061,14 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C40">
@@ -929,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>El Oro</t>
@@ -942,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -955,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -968,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Otzoloapan</t>
@@ -981,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Tejupilco</t>
@@ -994,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1007,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1038,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1051,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1064,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1077,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1097,7 +1302,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C53">
@@ -1108,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -1121,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Alpoyeca</t>
@@ -1134,9 +1349,14 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Atenango del Río</t>
+          <t>Atenango Del Río</t>
         </is>
       </c>
       <c r="C56">
@@ -1147,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Atlixtac</t>
@@ -1160,9 +1385,14 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Chilapa de Álvarez</t>
+          <t>Chilapa De Álvarez</t>
         </is>
       </c>
       <c r="C58">
@@ -1173,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Chilpancingo de los Bravo</t>
+          <t>Chilpancingo De Los Bravo</t>
         </is>
       </c>
       <c r="C59">
@@ -1186,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Metlatónoc</t>
@@ -1212,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Ometepec</t>
@@ -1225,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C63">
@@ -1238,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -1251,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Zirándaro</t>
@@ -1264,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1295,9 +1565,14 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C68">
@@ -1308,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -1321,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1352,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1409,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -1422,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Jojutla</t>
@@ -1435,9 +1745,14 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tlaltizapán de Zapata</t>
+          <t>Tlaltizapán De Zapata</t>
         </is>
       </c>
       <c r="C78">
@@ -1448,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>Tlaquiltenango</t>
@@ -1461,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1492,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1523,9 +1853,14 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Chalcatongo de Hidalgo</t>
+          <t>Chalcatongo De Hidalgo</t>
         </is>
       </c>
       <c r="C84">
@@ -1536,9 +1871,14 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Huajuapan de León</t>
+          <t>Heroica Ciudad De Huajuapan De León</t>
         </is>
       </c>
       <c r="C85">
@@ -1549,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Huautepec</t>
@@ -1562,9 +1907,14 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ixtlán de Juárez</t>
+          <t>Ixtlán De Juárez</t>
         </is>
       </c>
       <c r="C87">
@@ -1575,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -1588,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Magdalena Peñasco</t>
@@ -1601,9 +1961,14 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mariscala de Juárez</t>
+          <t>Mariscala De Juárez</t>
         </is>
       </c>
       <c r="C90">
@@ -1614,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Miahuatlán de Porfirio Díaz</t>
+          <t>Miahuatlán De Porfirio Díaz</t>
         </is>
       </c>
       <c r="C91">
@@ -1627,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Salina Cruz</t>
@@ -1640,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>San Antonio Huitepec</t>
@@ -1653,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>San Juan Bautista Cuicatlán</t>
@@ -1666,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>San Juan Bautista Guelache</t>
@@ -1679,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>San Juan Bautista Jayacatlán</t>
@@ -1692,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>San Pablo Huitzo</t>
@@ -1705,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>San Pedro Pochutla</t>
@@ -1718,6 +2123,11 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>Santa Catarina Quiané</t>
@@ -1731,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Santa Cruz Itundujia</t>
@@ -1744,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Santa Cruz Xoxocotlán</t>
@@ -1757,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -1770,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tataltepec de Valdés</t>
+          <t>Tataltepec De Valdés</t>
         </is>
       </c>
       <c r="C103">
@@ -1783,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1814,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Chichiquila</t>
@@ -1827,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Chietla</t>
@@ -1840,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -1853,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1866,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>Huehuetla</t>
@@ -1879,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Ixcaquixtla</t>
@@ -1892,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -1905,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C113">
@@ -1918,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -1931,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Libres</t>
@@ -1944,6 +2429,11 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -1957,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -1970,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Tehuacán</t>
@@ -1983,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Tehuitzingo</t>
@@ -1996,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tepanco de López</t>
+          <t>Tepanco De López</t>
         </is>
       </c>
       <c r="C120">
@@ -2009,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -2022,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -2035,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2066,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Tolimán</t>
@@ -2079,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2110,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2141,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -2154,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2185,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -2198,6 +2753,11 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2229,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Tepeyanco</t>
@@ -2242,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2273,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -2286,6 +2861,11 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>Jesús Carranza</t>
@@ -2299,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -2312,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -2325,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -2338,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Yanga</t>
@@ -2351,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2382,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2413,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2436,41 +3051,6 @@
       </c>
       <c r="D150">
         <v>1</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
